--- a/output/graficos_regionales/plot_i_peringrmin_a_2022_magallanes_y_la_antartica_chilena.xlsx
+++ b/output/graficos_regionales/plot_i_peringrmin_a_2022_magallanes_y_la_antartica_chilena.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,11 +385,6 @@
           <t>valor_previo</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>seleccionado</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -414,9 +409,6 @@
       <c r="F2">
         <v>3.1</v>
       </c>
-      <c r="G2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -441,9 +433,6 @@
       <c r="F3">
         <v>3.4</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,9 +457,6 @@
       <c r="F4">
         <v>3.7</v>
       </c>
-      <c r="G4" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -495,9 +481,6 @@
       <c r="F5">
         <v>4.18</v>
       </c>
-      <c r="G5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -522,9 +505,6 @@
       <c r="F6">
         <v>4.46</v>
       </c>
-      <c r="G6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -549,9 +529,6 @@
       <c r="F7">
         <v>5.24</v>
       </c>
-      <c r="G7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -576,9 +553,6 @@
       <c r="F8">
         <v>5.69</v>
       </c>
-      <c r="G8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -603,9 +577,6 @@
       <c r="F9">
         <v>5.72</v>
       </c>
-      <c r="G9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,9 +601,6 @@
       <c r="F10">
         <v>6.19</v>
       </c>
-      <c r="G10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -657,9 +625,6 @@
       <c r="F11">
         <v>6.17</v>
       </c>
-      <c r="G11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -684,9 +649,6 @@
       <c r="F12">
         <v>6.42</v>
       </c>
-      <c r="G12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -711,9 +673,6 @@
       <c r="F13">
         <v>6.76</v>
       </c>
-      <c r="G13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -738,9 +697,6 @@
       <c r="F14">
         <v>7.36</v>
       </c>
-      <c r="G14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -765,9 +721,6 @@
       <c r="F15">
         <v>7.45</v>
       </c>
-      <c r="G15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -792,9 +745,6 @@
       <c r="F16">
         <v>7.69</v>
       </c>
-      <c r="G16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -818,9 +768,6 @@
       </c>
       <c r="F17">
         <v>9.32</v>
-      </c>
-      <c r="G17" t="b">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
